--- a/Figure 6/Figure 6-C.xlsx
+++ b/Figure 6/Figure 6-C.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wench\Desktop\英文写作\英文写作\工程菌KR32\论文需要上传的数据\图6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wench\Desktop\英文写作\英文写作\工程菌KR32\论文需要上传的数据\iMetaOmics20260210\Figure 6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E82D59C1-422D-453E-AEDB-DA6F5399D827}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E34BACFC-CC96-4147-BFC1-40AB12621BA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22920" yWindow="3710" windowWidth="19500" windowHeight="15580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28790" yWindow="4080" windowWidth="16730" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -115,7 +115,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -129,6 +129,12 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -151,8 +157,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -440,151 +447,152 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B1" t="s">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="1">
         <v>0.47873896888063167</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="1">
         <v>0.46463074779377611</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="1">
         <v>0.49833372039015322</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="1">
         <v>0.51714468183929407</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="1">
         <v>0.45836042731072923</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="1">
         <v>0.44033325592196937</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="1">
         <v>0.4991175104505341</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="1">
         <v>0.5304691128657687</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="1">
         <v>0.54065838365072005</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="1">
         <v>0.5704424059451928</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="1">
         <v>0.55555039479795632</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="1">
         <v>0.56730724570366919</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="1">
         <v>0.53673943334881569</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="1">
         <v>0.50382025081281934</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="1">
         <v>0.45914421737111005</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="1">
         <v>0.45287389688806318</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="1">
         <v>0.41603576405016257</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="1">
         <v>0.41368439386902001</v>
       </c>
     </row>
